--- a/artfynd/A 57738-2021 artfynd.xlsx
+++ b/artfynd/A 57738-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 57738-2021 artfynd.xlsx
+++ b/artfynd/A 57738-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -791,6 +791,325 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>118912650</v>
+      </c>
+      <c r="B3" t="n">
+        <v>78510</v>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>6434</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Nästlav</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Bryoria furcellata</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Pottermyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>802882</v>
+      </c>
+      <c r="R3" t="n">
+        <v>7146783</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>118912655</v>
+      </c>
+      <c r="B4" t="n">
+        <v>97763</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Pottermyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>802882</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7146783</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>118913598</v>
+      </c>
+      <c r="B5" t="n">
+        <v>57443</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Pottermyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>803156</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7146658</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57738-2021 artfynd.xlsx
+++ b/artfynd/A 57738-2021 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118912650</v>
+        <v>118912655</v>
       </c>
       <c r="B3" t="n">
-        <v>78510</v>
+        <v>97763</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,26 +810,27 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>219790</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -900,10 +901,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118912655</v>
+        <v>118912650</v>
       </c>
       <c r="B4" t="n">
-        <v>97763</v>
+        <v>78510</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -916,27 +917,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>219790</v>
+        <v>6434</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>

--- a/artfynd/A 57738-2021 artfynd.xlsx
+++ b/artfynd/A 57738-2021 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118912655</v>
+        <v>118912650</v>
       </c>
       <c r="B3" t="n">
-        <v>97763</v>
+        <v>78517</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -810,27 +810,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>219790</v>
+        <v>6434</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -901,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118912650</v>
+        <v>118913598</v>
       </c>
       <c r="B4" t="n">
-        <v>78510</v>
+        <v>57443</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,30 +912,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6434</v>
+        <v>103021</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>802882</v>
+        <v>803156</v>
       </c>
       <c r="R4" t="n">
-        <v>7146783</v>
+        <v>7146658</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,7 +988,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1007,10 +1006,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118913598</v>
+        <v>118912655</v>
       </c>
       <c r="B5" t="n">
-        <v>57443</v>
+        <v>97770</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1019,31 +1018,31 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1051,10 +1050,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>803156</v>
+        <v>802882</v>
       </c>
       <c r="R5" t="n">
-        <v>7146658</v>
+        <v>7146783</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1095,6 +1094,7 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 57738-2021 artfynd.xlsx
+++ b/artfynd/A 57738-2021 artfynd.xlsx
@@ -794,10 +794,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>118912650</v>
+        <v>118913598</v>
       </c>
       <c r="B3" t="n">
-        <v>78517</v>
+        <v>57443</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -806,30 +806,31 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6434</v>
+        <v>103021</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -837,10 +838,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>802882</v>
+        <v>803156</v>
       </c>
       <c r="R3" t="n">
-        <v>7146783</v>
+        <v>7146658</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -881,7 +882,6 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
-      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -900,10 +900,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118913598</v>
+        <v>118912655</v>
       </c>
       <c r="B4" t="n">
-        <v>57443</v>
+        <v>97770</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -912,31 +912,31 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>219790</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +944,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>803156</v>
+        <v>802882</v>
       </c>
       <c r="R4" t="n">
-        <v>7146658</v>
+        <v>7146783</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -988,6 +988,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1006,10 +1007,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118912655</v>
+        <v>118912650</v>
       </c>
       <c r="B5" t="n">
-        <v>97770</v>
+        <v>78517</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1022,27 +1023,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>6434</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>

--- a/artfynd/A 57738-2021 artfynd.xlsx
+++ b/artfynd/A 57738-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>65060091</v>
       </c>
       <c r="B2" t="n">
-        <v>85703</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>89292</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -705,7 +700,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Berk. &amp; M.A. Curtis.) Pouzar</t>
+          <t>(Berk. &amp; M.A.Curtis.) Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -721,10 +716,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>802892.4640414957</v>
+        <v>802892</v>
       </c>
       <c r="R2" t="n">
-        <v>7147109.824183492</v>
+        <v>7147110</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -754,19 +749,9 @@
           <t>2015-05-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-05-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -797,12 +782,7 @@
         <v>118912650</v>
       </c>
       <c r="B3" t="n">
-        <v>78519</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -900,43 +880,42 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>118913598</v>
+        <v>118912679</v>
       </c>
       <c r="B4" t="n">
-        <v>57445</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57141</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>100138</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>äldre spillning</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -944,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>803156</v>
+        <v>802837</v>
       </c>
       <c r="R4" t="n">
-        <v>7146658</v>
+        <v>7146783</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1006,43 +985,38 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>118912655</v>
+        <v>118913598</v>
       </c>
       <c r="B5" t="n">
-        <v>97775</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1050,10 +1024,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>802882</v>
+        <v>803156</v>
       </c>
       <c r="R5" t="n">
-        <v>7146783</v>
+        <v>7146658</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1068,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1110,6 +1083,108 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>118912655</v>
+      </c>
+      <c r="B6" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Pottermyrberget, Vb</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>802882</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7146783</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lövånger</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-08-04</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Anton Lundberg</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 57738-2021 artfynd.xlsx
+++ b/artfynd/A 57738-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -776,6 +781,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65060091</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -877,6 +887,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912650</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -982,6 +997,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912679</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1083,6 +1103,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118913598</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1185,8 +1210,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118912655</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>